--- a/output/Tables/2019/Monte Carlo/1km_soc_value_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/1km_soc_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>7.576531636026038</v>
+        <v>4.831401840049748</v>
       </c>
       <c r="B2">
-        <v>7.897734861072361</v>
+        <v>5.003471718378767</v>
       </c>
       <c r="C2">
-        <v>8.193185442870011</v>
+        <v>5.161185954432841</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/Monte Carlo/1km_soc_value_1000replicate.xlsx
+++ b/output/Tables/2019/Monte Carlo/1km_soc_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>4.831401840049748</v>
+        <v>4.981550238054954</v>
       </c>
       <c r="B2">
-        <v>5.003471718378767</v>
+        <v>5.164146284583915</v>
       </c>
       <c r="C2">
-        <v>5.161185954432841</v>
+        <v>5.331507038272234</v>
       </c>
       <c r="D2">
         <v>1</v>
